--- a/final_outputs/excel_tables/table_qlp_full.xlsx
+++ b/final_outputs/excel_tables/table_qlp_full.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.000005, 0.000034]</t>
+          <t>[-0.000037, 0.000036]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.000003</t>
+          <t>-0.000006</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[-0.000017, 0.000013]</t>
+          <t>[-0.000021, 0.000008]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.000015</t>
+          <t>-0.000018</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[-0.000038, 0.000017]</t>
+          <t>[-0.000046, 0.000011]</t>
         </is>
       </c>
     </row>
@@ -521,32 +521,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.000031</t>
+          <t>0.000014</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.000004, 0.000078]</t>
+          <t>[-0.000068, 0.000060]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.000007</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[-0.000028, 0.000034]</t>
+          <t>[-0.000039, 0.000029]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.000019</t>
+          <t>0.000009</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[-0.000040, 0.000068]</t>
+          <t>[-0.000055, 0.000068]</t>
         </is>
       </c>
     </row>
@@ -561,32 +561,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.000029</t>
+          <t>-0.000016</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[-0.000030, 0.000110]</t>
+          <t>[-0.000107, 0.000088]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.000017</t>
+          <t>0.000006</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000057]</t>
+          <t>[-0.000042, 0.000051]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.000027</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[-0.000036, 0.000089]</t>
+          <t>[-0.000060, 0.000098]</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.000017</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[-0.000070, 0.000095]</t>
+          <t>[-0.000104, 0.000071]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.000038</t>
+          <t>0.000031</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[-0.000013, 0.000092]</t>
+          <t>[-0.000041, 0.000084]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.000000</t>
+          <t>-0.000026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[-0.000060, 0.000110]</t>
+          <t>[-0.000115, 0.000080]</t>
         </is>
       </c>
     </row>
@@ -641,32 +641,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.000002</t>
+          <t>-0.000009</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[-0.000022, 0.000027]</t>
+          <t>[-0.000039, 0.000020]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000003</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[-0.000005, 0.000018]</t>
+          <t>[-0.000011, 0.000016]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.000001</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[-0.000019, 0.000020]</t>
+          <t>[-0.000031, 0.000017]</t>
         </is>
       </c>
     </row>
@@ -681,32 +681,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>-0.000016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[-0.000032, 0.000058]</t>
+          <t>[-0.000076, 0.000046]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.000019</t>
+          <t>0.000009</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[-0.000009, 0.000051]</t>
+          <t>[-0.000019, 0.000045]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.000010</t>
+          <t>-0.000027</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[-0.000056, 0.000054]</t>
+          <t>[-0.000077, 0.000048]</t>
         </is>
       </c>
     </row>
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.000015</t>
+          <t>-0.000063</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[-0.000088, 0.000049]</t>
+          <t>[-0.000140, 0.000029]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.000004</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[-0.000037, 0.000045]</t>
+          <t>[-0.000047, 0.000035]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.000018</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[-0.000074, 0.000044]</t>
+          <t>[-0.000087, 0.000033]</t>
         </is>
       </c>
     </row>
@@ -761,32 +761,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>-0.000013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[-0.000086, 0.000056]</t>
+          <t>[-0.000098, 0.000061]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.000045</t>
+          <t>-0.000064</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[-0.000097, 0.000005]</t>
+          <t>[-0.000108, 0.000002]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.000011</t>
+          <t>-0.000021</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[-0.000094, 0.000050]</t>
+          <t>[-0.000112, 0.000048]</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000020</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[-0.000033, 0.000004]</t>
+          <t>[-0.000063, 0.000005]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[-0.000016, 0.000006]</t>
+          <t>[-0.000017, 0.000006]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.000028</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[-0.000051, 0.000009]</t>
+          <t>[-0.000062, 0.000006]</t>
         </is>
       </c>
     </row>
@@ -841,32 +841,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.000010</t>
+          <t>-0.000038</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[-0.000046, 0.000039]</t>
+          <t>[-0.000127, 0.000040]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.000003</t>
+          <t>-0.000014</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[-0.000025, 0.000015]</t>
+          <t>[-0.000039, 0.000011]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.000001</t>
+          <t>-0.000040</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[-0.000068, 0.000036]</t>
+          <t>[-0.000107, 0.000024]</t>
         </is>
       </c>
     </row>
@@ -881,32 +881,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000036</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[-0.000051, 0.000069]</t>
+          <t>[-0.000183, 0.000036]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.000007</t>
+          <t>-0.000011</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000060]</t>
+          <t>[-0.000058, 0.000051]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.000003</t>
+          <t>-0.000036</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[-0.000071, 0.000070]</t>
+          <t>[-0.000149, 0.000038]</t>
         </is>
       </c>
     </row>
@@ -921,32 +921,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.000029</t>
+          <t>-0.000005</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[-0.000045, 0.000095]</t>
+          <t>[-0.000187, 0.000068]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.000027</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[-0.000023, 0.000076]</t>
+          <t>[-0.000054, 0.000065]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.000033</t>
+          <t>-0.000038</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[-0.000127, 0.000019]</t>
+          <t>[-0.000151, 0.000001]</t>
         </is>
       </c>
     </row>
@@ -961,32 +961,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.000016</t>
+          <t>0.000003</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[-0.000008, 0.000031]</t>
+          <t>[-0.000068, 0.000026]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.000010</t>
+          <t>-0.000016</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[-0.000024, 0.000009]</t>
+          <t>[-0.000031, 0.000004]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.000025*</t>
+          <t>-0.000032*</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[-0.000047, -0.000003]</t>
+          <t>[-0.000068, -0.000011]</t>
         </is>
       </c>
     </row>
@@ -1001,32 +1001,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.000040*</t>
+          <t>-0.000065*</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[-0.000093, -0.000001]</t>
+          <t>[-0.000172, -0.000016]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.000002</t>
+          <t>-0.000015</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[-0.000041, 0.000029]</t>
+          <t>[-0.000057, 0.000024]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.000019</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[-0.000082, 0.000025]</t>
+          <t>[-0.000105, 0.000038]</t>
         </is>
       </c>
     </row>
@@ -1041,32 +1041,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.000037</t>
+          <t>-0.000099</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[-0.000098, 0.000045]</t>
+          <t>[-0.000193, 0.000007]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.000022</t>
+          <t>-0.000026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[-0.000065, 0.000016]</t>
+          <t>[-0.000087, 0.000015]</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.000035</t>
+          <t>-0.000104</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[-0.000136, 0.000031]</t>
+          <t>[-0.000179, 0.000025]</t>
         </is>
       </c>
     </row>
@@ -1081,32 +1081,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.000039</t>
+          <t>-0.000146</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[-0.000120, 0.000052]</t>
+          <t>[-0.000303, 0.000006]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-0.000027</t>
+          <t>-0.000044</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[-0.000072, 0.000023]</t>
+          <t>[-0.000121, 0.000007]</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.000054</t>
+          <t>-0.000104</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[-0.000102, 0.000064]</t>
+          <t>[-0.000214, 0.000027]</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.000004</t>
+          <t>0.000015</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[-0.000026, 0.000041]</t>
+          <t>[-0.000023, 0.000046]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-0.000006</t>
+          <t>-0.000005</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[-0.000018, 0.000007]</t>
+          <t>[-0.000018, 0.000010]</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.000022*</t>
+          <t>-0.000017</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[-0.000037, -0.000001]</t>
+          <t>[-0.000034, 0.000011]</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[-0.000056, 0.000046]</t>
+          <t>[-0.000049, 0.000059]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[-0.000048, 0.000009]</t>
+          <t>[-0.000046, 0.000013]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000015</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[-0.000037, 0.000056]</t>
+          <t>[-0.000047, 0.000061]</t>
         </is>
       </c>
     </row>
@@ -1201,32 +1201,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.000011</t>
+          <t>0.000037</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[-0.000082, 0.000059]</t>
+          <t>[-0.000036, 0.000144]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.000027</t>
+          <t>0.000030</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[-0.000018, 0.000068]</t>
+          <t>[-0.000011, 0.000070]</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.000017</t>
+          <t>0.000021</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[-0.000051, 0.000076]</t>
+          <t>[-0.000045, 0.000098]</t>
         </is>
       </c>
     </row>
@@ -1241,32 +1241,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.000037</t>
+          <t>0.000060</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[-0.000078, 0.000101]</t>
+          <t>[-0.000014, 0.000195]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-0.000004</t>
+          <t>0.000012</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[-0.000040, 0.000059]</t>
+          <t>[-0.000035, 0.000065]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>0.000040</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[-0.000128, 0.000083]</t>
+          <t>[-0.000098, 0.000113]</t>
         </is>
       </c>
     </row>

--- a/final_outputs/excel_tables/table_qlp_full.xlsx
+++ b/final_outputs/excel_tables/table_qlp_full.xlsx
@@ -481,32 +481,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.000015</t>
+          <t>0.000025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.000037, 0.000036]</t>
+          <t>[-0.000005, 0.000044]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.000006</t>
+          <t>-0.000002</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[-0.000021, 0.000008]</t>
+          <t>[-0.000017, 0.000014]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.000018</t>
+          <t>-0.000009</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[-0.000046, 0.000011]</t>
+          <t>[-0.000034, 0.000023]</t>
         </is>
       </c>
     </row>
@@ -521,32 +521,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.000014</t>
+          <t>0.000035</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.000068, 0.000060]</t>
+          <t>[-0.000028, 0.000071]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>0.000001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[-0.000039, 0.000029]</t>
+          <t>[-0.000034, 0.000036]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.000009</t>
+          <t>0.000013</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[-0.000055, 0.000068]</t>
+          <t>[-0.000041, 0.000068]</t>
         </is>
       </c>
     </row>
@@ -561,32 +561,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>0.000030</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[-0.000107, 0.000088]</t>
+          <t>[-0.000052, 0.000103]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.000006</t>
+          <t>0.000013</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[-0.000042, 0.000051]</t>
+          <t>[-0.000038, 0.000058]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000013</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[-0.000060, 0.000098]</t>
+          <t>[-0.000041, 0.000109]</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>0.000027</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[-0.000104, 0.000071]</t>
+          <t>[-0.000074, 0.000090]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.000031</t>
+          <t>0.000033</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[-0.000041, 0.000084]</t>
+          <t>[-0.000024, 0.000084]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.000026</t>
+          <t>0.000025</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[-0.000115, 0.000080]</t>
+          <t>[-0.000067, 0.000088]</t>
         </is>
       </c>
     </row>
@@ -641,32 +641,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.000009</t>
+          <t>0.000007</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[-0.000039, 0.000020]</t>
+          <t>[-0.000027, 0.000030]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.000003</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[-0.000011, 0.000016]</t>
+          <t>[-0.000007, 0.000019]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000017]</t>
+          <t>[-0.000016, 0.000028]</t>
         </is>
       </c>
     </row>
@@ -681,32 +681,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>0.000012</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[-0.000076, 0.000046]</t>
+          <t>[-0.000037, 0.000060]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.000009</t>
+          <t>0.000019</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[-0.000019, 0.000045]</t>
+          <t>[-0.000011, 0.000048]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.000027</t>
+          <t>-0.000011</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[-0.000077, 0.000048]</t>
+          <t>[-0.000057, 0.000063]</t>
         </is>
       </c>
     </row>
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.000063</t>
+          <t>-0.000048</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[-0.000140, 0.000029]</t>
+          <t>[-0.000095, 0.000053]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000004</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[-0.000047, 0.000035]</t>
+          <t>[-0.000038, 0.000040]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.000034</t>
+          <t>-0.000028</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[-0.000087, 0.000033]</t>
+          <t>[-0.000076, 0.000044]</t>
         </is>
       </c>
     </row>
@@ -761,32 +761,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.000013</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[-0.000098, 0.000061]</t>
+          <t>[-0.000072, 0.000088]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.000064</t>
+          <t>-0.000046</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[-0.000108, 0.000002]</t>
+          <t>[-0.000096, 0.000006]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.000021</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[-0.000112, 0.000048]</t>
+          <t>[-0.000100, 0.000051]</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[-0.000063, 0.000005]</t>
+          <t>[-0.000051, 0.000003]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[-0.000017, 0.000006]</t>
+          <t>[-0.000016, 0.000009]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.000034</t>
+          <t>-0.000018</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[-0.000062, 0.000006]</t>
+          <t>[-0.000045, 0.000016]</t>
         </is>
       </c>
     </row>
@@ -841,32 +841,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.000038</t>
+          <t>-0.000020</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[-0.000127, 0.000040]</t>
+          <t>[-0.000078, 0.000037]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.000014</t>
+          <t>-0.000002</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>[-0.000039, 0.000011]</t>
+          <t>[-0.000028, 0.000017]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.000040</t>
+          <t>-0.000003</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[-0.000107, 0.000024]</t>
+          <t>[-0.000071, 0.000045]</t>
         </is>
       </c>
     </row>
@@ -881,32 +881,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.000036</t>
+          <t>-0.000023</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[-0.000183, 0.000036]</t>
+          <t>[-0.000089, 0.000060]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.000011</t>
+          <t>0.000006</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[-0.000058, 0.000051]</t>
+          <t>[-0.000042, 0.000061]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.000036</t>
+          <t>-0.000010</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[-0.000149, 0.000038]</t>
+          <t>[-0.000076, 0.000067]</t>
         </is>
       </c>
     </row>
@@ -921,32 +921,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.000005</t>
+          <t>0.000027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[-0.000187, 0.000068]</t>
+          <t>[-0.000090, 0.000099]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000023</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[-0.000054, 0.000065]</t>
+          <t>[-0.000029, 0.000072]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.000038</t>
+          <t>-0.000025</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[-0.000151, 0.000001]</t>
+          <t>[-0.000122, 0.000016]</t>
         </is>
       </c>
     </row>
@@ -961,32 +961,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.000003</t>
+          <t>0.000024</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[-0.000068, 0.000026]</t>
+          <t>[-0.000010, 0.000045]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>-0.000010</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000004]</t>
+          <t>[-0.000023, 0.000012]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.000032*</t>
+          <t>-0.000021</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[-0.000068, -0.000011]</t>
+          <t>[-0.000042, 0.000012]</t>
         </is>
       </c>
     </row>
@@ -1001,32 +1001,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.000065*</t>
+          <t>-0.000050*</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[-0.000172, -0.000016]</t>
+          <t>[-0.000155, -0.000013]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-0.000015</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[-0.000057, 0.000024]</t>
+          <t>[-0.000049, 0.000024]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000029</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[-0.000105, 0.000038]</t>
+          <t>[-0.000090, 0.000021]</t>
         </is>
       </c>
     </row>
@@ -1041,32 +1041,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.000099</t>
+          <t>-0.000061</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[-0.000193, 0.000007]</t>
+          <t>[-0.000188, 0.000034]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.000026</t>
+          <t>-0.000028</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[-0.000087, 0.000015]</t>
+          <t>[-0.000079, 0.000018]</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.000104</t>
+          <t>-0.000063</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[-0.000179, 0.000025]</t>
+          <t>[-0.000155, 0.000031]</t>
         </is>
       </c>
     </row>
@@ -1081,32 +1081,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.000146</t>
+          <t>-0.000048</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[-0.000303, 0.000006]</t>
+          <t>[-0.000156, 0.000060]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-0.000044</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[-0.000121, 0.000007]</t>
+          <t>[-0.000084, 0.000012]</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.000104</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[-0.000214, 0.000027]</t>
+          <t>[-0.000135, 0.000054]</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.000015</t>
+          <t>0.000008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[-0.000023, 0.000046]</t>
+          <t>[-0.000020, 0.000045]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[-0.000018, 0.000010]</t>
+          <t>[-0.000018, 0.000008]</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.000017</t>
+          <t>-0.000025</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[-0.000034, 0.000011]</t>
+          <t>[-0.000040, 0.000000]</t>
         </is>
       </c>
     </row>
@@ -1161,19 +1161,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>-0.000015</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[-0.000051, 0.000050]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>-0.000022</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[-0.000049, 0.000059]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-0.000023</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>[-0.000046, 0.000013]</t>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.000015</t>
+          <t>0.000017</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[-0.000047, 0.000061]</t>
+          <t>[-0.000053, 0.000056]</t>
         </is>
       </c>
     </row>
@@ -1201,32 +1201,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.000037</t>
+          <t>0.000016</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[-0.000036, 0.000144]</t>
+          <t>[-0.000053, 0.000120]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.000030</t>
+          <t>0.000029</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[-0.000011, 0.000070]</t>
+          <t>[-0.000020, 0.000073]</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.000021</t>
+          <t>0.000010</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[-0.000045, 0.000098]</t>
+          <t>[-0.000049, 0.000082]</t>
         </is>
       </c>
     </row>
@@ -1241,32 +1241,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.000060</t>
+          <t>0.000039</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[-0.000014, 0.000195]</t>
+          <t>[-0.000078, 0.000104]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.000012</t>
+          <t>0.000000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[-0.000035, 0.000065]</t>
+          <t>[-0.000037, 0.000061]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.000040</t>
+          <t>-0.000006</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[-0.000098, 0.000113]</t>
+          <t>[-0.000129, 0.000088]</t>
         </is>
       </c>
     </row>
